--- a/excels/Publications.xlsx
+++ b/excels/Publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE22A372-8186-48C9-BE0E-E1D7F44798D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ED9B59-78A4-41F9-81DC-84E6978A56FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journals" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="300">
   <si>
     <t>Title</t>
   </si>
@@ -1302,13 +1302,516 @@
   </si>
   <si>
     <t>Evaluation of Rejuvenated Recycled Bitumen Binders based on Rutting Performance and Chemical Characterization using FTIR By Khatri K., Tahir Ansari. M., Vishnu Radhakrishnan and Venkaiah Chowdary , Transportation Planning and Implementation Methodologies for Developing Countries (TPMDC), 2020</t>
+  </si>
+  <si>
+    <r>
+      <t>Comparative assessment of pollutant concentrations at adults and children breathing height at urban intersections under mixed traffic flow</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Rohith, C., and Kadali, B.R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Springer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Innovative Infrastructure Solutions</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, vol., pp.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Real-time traffic data collection using roadside LiDAR: a novel background filtering approach</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Ansari, A., and Kadali, B. R.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Springer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Innovative Infrastructure Solutions</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, vol.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10:10</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, pp.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Predicting Near-Road Exposure from Vehicular Emission in Urban Areas Using the LSTM Technique</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Rohith, C., and Kadali, B. R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ASCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Journal of Environmental Engineering</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, vol.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>152(3),</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, pp.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> 1-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Predicting Near-Road Exposure from Vehicular Emission in Urban Areas Using the LSTM Technique</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> Rohith, C., and Kadali, B.R., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ASCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Journal of Environmental Engineering</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, vol.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>152(3)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, pp.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>04025106</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF6C757D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212529"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>International Conference on ‘Safe System Perspective for Indian Mixed Traffic Conditions, 2026</t>
+  </si>
+  <si>
+    <t>Preparation Enhancing Green Signal Timings for Improved Traffic Flow and Environmental Sustainability on Urban Corridors, By Suresh B. and Ravi Shankar K.V.R. , Budapest University of Technology and Economics, Hungary, Periodica Polytechnica Transportation Engineering, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>9th Conference on Transportation Systems Engineering and Management (CTSEM-2023), 2023</t>
+  </si>
+  <si>
+    <t>SPARC Sponsored International Conference Safe System Perspective for Indian Mixed Traffic Conditions (SafeInd 2026), 2026</t>
+  </si>
+  <si>
+    <t>Integrating environmental sustainability into rural road maintenance: a life cycle-based framework for planning and implementation, By Raji Reddy Myakala &amp; Shankar Sabavath, Taylor and Francis , Australian Jounal of Civil Engineeirng , vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Assessing the influence of vehicular fuel type on urban road traffic noise using frequency-domain acoustic monitoring, By Nallavelli Srinidhi Reddy, Venkaiah Chowdary, and Boddu Sudhir Kumar, Springer, Environmental Monitoring and Assessment, vol.198, pp.445, 2026</t>
+  </si>
+  <si>
+    <t>Quantification of Tire-Pavement Interaction Noise Using Frequency Analysis, By Akash Yadav, Dhawal Kanholkar, Nallavelli Srinidhi Reddy, Venkaiah Chowdary, and Boddu Sudhir Kumar , Springer, Transportation in Developing Economies, vol.14, pp.4, 2026</t>
+  </si>
+  <si>
+    <t>Research Scholars' Confluence 2025, 2025</t>
+  </si>
+  <si>
+    <t>Evaluation of Ravelling Potential of Dense-Graded Bituminous Mixtures under Controlled Ageing and Moisture Conditioning using Cantabro Test , By Onkar Bandari, Jithin Kurien Andrews, Vishnu Radhakrishnan, ASCE, Journal of Materials in Civil Engineering, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Evaluation of temperature dependency of falling weight deflectometer measurements for asphalt mixes with waste low-density polyethylene, By Rout B, Vishnu Radhakrishnan, Govindaraju, Taylor &amp; Francis Online, International Journal of Pavement Engineering, vol.27, pp.1, 2026</t>
+  </si>
+  <si>
+    <t>Fatigue performance of glass fibre-reinforced admixture-stabilised rock sludge dust as a base layer for low-volume roads, By Kola V, G. V Ramana, Vishnu Radhakrishnan, Taylor &amp; Francis Online, International Journal of Pavement Engineering, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Fatigue characterisation of cementitious full depth reclamation mixes, By Ammu B Crusho, Vishnu Radhakrishnan, Bharath G, A Veeraraghavan, Taylor &amp; Francis Online, International Journal of Pavement Engineering, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Development of performance based binder rutting specifications for India, By Harshavardhan Goud, E., Radhakrishnan Vishnu., Bharath G., Sudhakar Reddy, K, Indian Roads Congress, Indian Highways, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Validation of load-deflection linearity in pavements using deflection bowl parameters, By Jithin Kurien Andrews., Radhakrishnan Vishnu., Lakshmi P., Joe G. Philip, Springer Nature, Transportation Infrastructure Geotechnology, vol.13, pp.81, 2026</t>
+  </si>
+  <si>
+    <t>Study on the cracking potential of emulsion treated base layer mixes using the concepts of fracture energy and post peak slope, By Jithin Kurien Andrews., Radhakrishnan Vishnu., Lakshmi P., Joe G. Philip, Springer Nature, Transportation Infrastructure Geotechnology, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Fatigue performance of RAP-incorporated open-graded cement-stabilised macadam with GGBFS and FCC unit residue. Innovative Infrastructure Solutions, By Saranya Ullas., Bindu, C. S., Radhakrishnan Vishnu, Springer Nature, Innovative Infrastructure Solutions, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Mechanical and microstructure characterization of cementitious full depth reclamation mixtures, By Crusho, Ammu B., Radhakrishnan Vishnu., Sridhar Reddy, K., Veeraragavan A., Asadevi, H, Springer Nature, Innovative Infrastructure Solutions, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Influence of aged binder availability on compaction characteristics and mechanical properties of recycled asphalt mixes, By Munagapati, P. T., Harshavardhan Goud, E., Radhakrishnan Vishnu, Springer Nature, International Journal of Pavement Research and Technology, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Laboratory and mechanistic evaluation of influence of the degree of compaction on the performance of cement-stabilized full-depth reclamation mixes, By Kalava Lakshman Sai., Sachin Gowda, M. K., Bharath G., Gopala Raju, S. S. S. V., Radhakrishnan Vishnu., Anil Kumar, R, SAGE Publishing, Transportation Research Record, vol., pp., 2026</t>
+  </si>
+  <si>
+    <t>Evaluation of Factors Affecting the Service Quality of Mobility Hubs in Developing Economies, By Ganga Aishwarya, Manoj Kumar Mina, Rahul Meena, Anusree Achipra, Vishnu Radhakrishnan &amp; Mithun Mohan , Springer Nature, Transportation in Developing Economies, vol.12, pp.17, 2026</t>
+  </si>
+  <si>
+    <t>Effect of RAP fractionation size and ageing on recycled asphalt binder availability and recycled mixture performance, By Anusree A, Vishnu Radhakrishnan, Springer Nature, Innovative Infrastructure Solutions, vol., pp., 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1360,6 +1863,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212529"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF6C757D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6C757D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1381,7 +1903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1397,6 +1919,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1699,7 +2224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="255.7109375" bestFit="1" customWidth="1"/>
@@ -2789,6 +3314,111 @@
         <v>271</v>
       </c>
     </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2797,7 +3427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7B7067-AE32-467E-8CFB-6BBF9F992D15}">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="247.7109375" customWidth="1"/>
@@ -3234,6 +3864,26 @@
         <v>274</v>
       </c>
     </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>286</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
